--- a/artfynd/A 37891-2025 artfynd.xlsx
+++ b/artfynd/A 37891-2025 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>126830726</v>
       </c>
       <c r="B6" t="n">
-        <v>58516</v>
+        <v>58520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>126847530</v>
       </c>
       <c r="B7" t="n">
-        <v>41361</v>
+        <v>41365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>126895453</v>
       </c>
       <c r="B8" t="n">
-        <v>56964</v>
+        <v>56968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127007195</v>
       </c>
       <c r="B9" t="n">
-        <v>56233</v>
+        <v>56237</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37891-2025 artfynd.xlsx
+++ b/artfynd/A 37891-2025 artfynd.xlsx
@@ -1373,7 +1373,7 @@
         <v>126895453</v>
       </c>
       <c r="B8" t="n">
-        <v>56968</v>
+        <v>56970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127007195</v>
       </c>
       <c r="B9" t="n">
-        <v>56237</v>
+        <v>56239</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37891-2025 artfynd.xlsx
+++ b/artfynd/A 37891-2025 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>126830726</v>
       </c>
       <c r="B6" t="n">
-        <v>58520</v>
+        <v>58516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>126847530</v>
       </c>
       <c r="B7" t="n">
-        <v>41365</v>
+        <v>41361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>126895453</v>
       </c>
       <c r="B8" t="n">
-        <v>56970</v>
+        <v>56964</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127007195</v>
       </c>
       <c r="B9" t="n">
-        <v>56239</v>
+        <v>56233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37891-2025 artfynd.xlsx
+++ b/artfynd/A 37891-2025 artfynd.xlsx
@@ -1599,7 +1599,7 @@
         <v>132205543</v>
       </c>
       <c r="B10" t="n">
-        <v>58595</v>
+        <v>58597</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>132212728</v>
       </c>
       <c r="B11" t="n">
-        <v>58078</v>
+        <v>58080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37891-2025 artfynd.xlsx
+++ b/artfynd/A 37891-2025 artfynd.xlsx
@@ -1599,7 +1599,7 @@
         <v>132205543</v>
       </c>
       <c r="B10" t="n">
-        <v>58597</v>
+        <v>58598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>132212728</v>
       </c>
       <c r="B11" t="n">
-        <v>58080</v>
+        <v>58081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37891-2025 artfynd.xlsx
+++ b/artfynd/A 37891-2025 artfynd.xlsx
@@ -1599,7 +1599,7 @@
         <v>132205543</v>
       </c>
       <c r="B10" t="n">
-        <v>58598</v>
+        <v>58602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>132212728</v>
       </c>
       <c r="B11" t="n">
-        <v>58081</v>
+        <v>58085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37891-2025 artfynd.xlsx
+++ b/artfynd/A 37891-2025 artfynd.xlsx
@@ -1599,7 +1599,7 @@
         <v>132205543</v>
       </c>
       <c r="B10" t="n">
-        <v>58602</v>
+        <v>58603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>132212728</v>
       </c>
       <c r="B11" t="n">
-        <v>58085</v>
+        <v>58086</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
